--- a/output/pdf_financials_xlsx/BAC.xlsx
+++ b/output/pdf_financials_xlsx/BAC.xlsx
@@ -1922,13 +1922,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.20509</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.233731</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.598606</v>
       </c>
     </row>
     <row r="93">
@@ -2788,7 +2788,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="n">
         <v>0.284946</v>
       </c>
@@ -3287,7 +3291,11 @@
           <t>Warrant reserve (note 10)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>1.20509</v>
       </c>

--- a/output/pdf_financials_xlsx/BAC.xlsx
+++ b/output/pdf_financials_xlsx/BAC.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>2.004973</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>1.769484</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>1.740061</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-2.004973</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>-1.769484</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>-1.740061</v>
       </c>
     </row>
     <row r="12">
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.073199</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.005361</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.019425</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.073199</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.755</v>
+        <v>0.760361</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.3725</v>
+        <v>0.391925</v>
       </c>
     </row>
     <row r="37">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.374119</v>
+        <v>0.30092</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.029407</v>
+        <v>0.024046</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.044074</v>
+        <v>0.024649</v>
       </c>
     </row>
     <row r="49">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">

--- a/output/pdf_financials_xlsx/BAC.xlsx
+++ b/output/pdf_financials_xlsx/BAC.xlsx
@@ -1468,13 +1468,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.353132</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.82552</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.638051</v>
       </c>
     </row>
     <row r="65">
@@ -2287,7 +2287,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.331055</v>
       </c>
     </row>
     <row r="116">
@@ -3556,7 +3556,11 @@
           <t>Gross proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -3897,7 +3901,11 @@
           <t>Gross proceeds from debenture private placement</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
         <v>0.4</v>
       </c>
